--- a/artfynd/A 12594-2026 artfynd.xlsx
+++ b/artfynd/A 12594-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132365730</v>
       </c>
       <c r="B2" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>132365756</v>
       </c>
       <c r="B3" t="n">
-        <v>57948</v>
+        <v>57949</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12594-2026 artfynd.xlsx
+++ b/artfynd/A 12594-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132365730</v>
       </c>
       <c r="B2" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>132365756</v>
       </c>
       <c r="B3" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 12594-2026 artfynd.xlsx
+++ b/artfynd/A 12594-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132365730</v>
       </c>
       <c r="B2" t="n">
-        <v>57141</v>
+        <v>57142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -783,7 +783,7 @@
         <v>132365756</v>
       </c>
       <c r="B3" t="n">
-        <v>57953</v>
+        <v>57954</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
